--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.88909857854769</v>
+        <v>10.544478519014</v>
       </c>
       <c r="D2" t="n">
-        <v>48.34511350695125</v>
+        <v>7.856080944879579</v>
       </c>
       <c r="E2" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F2" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.83837298605605</v>
+        <v>9.236235610234109</v>
       </c>
       <c r="D3" t="n">
-        <v>22.94558781116753</v>
+        <v>3.728658019314724</v>
       </c>
       <c r="E3" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F3" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.18024645173118</v>
+        <v>8.641790048406317</v>
       </c>
       <c r="D4" t="n">
-        <v>20.94039159137192</v>
+        <v>3.402813633597938</v>
       </c>
       <c r="E4" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F4" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.01119893601873</v>
+        <v>8.776819827103044</v>
       </c>
       <c r="D5" t="n">
-        <v>18.9010581714358</v>
+        <v>3.071421952858318</v>
       </c>
       <c r="E5" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F5" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.0522645804615</v>
+        <v>5.533492994324994</v>
       </c>
       <c r="D6" t="n">
-        <v>35.09502757799464</v>
+        <v>5.70294198142413</v>
       </c>
       <c r="E6" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F6" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.88741243415772</v>
+        <v>9.40670452055063</v>
       </c>
       <c r="D7" t="n">
-        <v>41.2818597619537</v>
+        <v>6.708302211317477</v>
       </c>
       <c r="E7" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F7" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>57.80791599476011</v>
+        <v>9.393786349148519</v>
       </c>
       <c r="D8" t="n">
-        <v>58.45101461534788</v>
+        <v>9.498289874994031</v>
       </c>
       <c r="E8" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F8" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.39348020515529</v>
+        <v>7.538940533337734</v>
       </c>
       <c r="D9" t="n">
-        <v>40.71671829220061</v>
+        <v>6.616466722482599</v>
       </c>
       <c r="E9" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F9" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.65287415463647</v>
+        <v>6.931092050128427</v>
       </c>
       <c r="D10" t="n">
-        <v>43.19098778161117</v>
+        <v>7.018535514511815</v>
       </c>
       <c r="E10" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F10" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.46226105873152</v>
+        <v>2.837617422043872</v>
       </c>
       <c r="D11" t="n">
-        <v>19.80123225796953</v>
+        <v>3.21770024192005</v>
       </c>
       <c r="E11" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F11" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.89903505497082</v>
+        <v>5.996093196432759</v>
       </c>
       <c r="D12" t="n">
-        <v>35.93601088565642</v>
+        <v>5.839601768919167</v>
       </c>
       <c r="E12" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F12" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.45518151966967</v>
+        <v>5.436466996946322</v>
       </c>
       <c r="D13" t="n">
-        <v>32.41473498866803</v>
+        <v>5.267394435658555</v>
       </c>
       <c r="E13" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F13" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.83140929207372</v>
+        <v>6.472604009961979</v>
       </c>
       <c r="D14" t="n">
-        <v>39.10521230448108</v>
+        <v>6.354596999478176</v>
       </c>
       <c r="E14" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F14" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>36.06328288124953</v>
+        <v>5.860283468203049</v>
       </c>
       <c r="D15" t="n">
-        <v>35.3372948009862</v>
+        <v>5.742310405160258</v>
       </c>
       <c r="E15" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F15" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>55.87633077678309</v>
+        <v>9.079903751227253</v>
       </c>
       <c r="D16" t="n">
-        <v>54.83069193594853</v>
+        <v>8.909987439591637</v>
       </c>
       <c r="E16" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F16" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>87.719099277393</v>
+        <v>14.25435363257636</v>
       </c>
       <c r="D17" t="n">
-        <v>87.34341430444438</v>
+        <v>14.19330482447221</v>
       </c>
       <c r="E17" t="n">
-        <v>15.73036020400288</v>
+        <v>2.556183533150467</v>
       </c>
       <c r="F17" t="n">
-        <v>16.78894735415692</v>
+        <v>2.728203945050501</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
